--- a/Assets/StreamingAssets/Localization/Buildings.xlsx
+++ b/Assets/StreamingAssets/Localization/Buildings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\IdleProject\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E5C64D1-6F33-43EC-B844-F8459E1DDE8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCDBFF05-11F0-47A7-9884-21857C99EC73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>key</t>
   </si>
@@ -88,6 +88,15 @@
   </si>
   <si>
     <t>Это Дом</t>
+  </si>
+  <si>
+    <t>progress_bar</t>
+  </si>
+  <si>
+    <t>Progress Bar</t>
+  </si>
+  <si>
+    <t>Шкала Прогресса</t>
   </si>
 </sst>
 </file>
@@ -420,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.44140625" style="1" customWidth="1"/>
@@ -506,6 +515,17 @@
         <v>20</v>
       </c>
     </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
